--- a/dcf/RGEN.xlsx
+++ b/dcf/RGEN.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>103.5232544584293</v>
+        <v>93.76795233955923</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>99.78717842090096</v>
+        <v>90.44443536110788</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>96.22361317702004</v>
+        <v>87.27370244164318</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>92.82360267101375</v>
+        <v>84.24783699017648</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>89.57869993938642</v>
+        <v>81.35937197125953</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>86.48093583919729</v>
+        <v>78.60126230633286</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>83.52278983482026</v>
+        <v>75.96685909111929</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>110.3660095341689</v>
+        <v>99.79858425916308</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>106.3191212912886</v>
+        <v>96.20114340270484</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>102.4602028981459</v>
+        <v>92.77011092410368</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>98.7794632911049</v>
+        <v>89.49683432628987</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>95.26766913989444</v>
+        <v>86.37315353591957</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>91.91611053813233</v>
+        <v>83.39137062750176</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>88.71656895469241</v>
+        <v>80.54422154191366</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>117.2087646099084</v>
+        <v>105.8292161787669</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>112.8510641616762</v>
+        <v>101.9578514443018</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>108.6967926192717</v>
+        <v>98.26651940656417</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>104.7353239111961</v>
+        <v>94.74583166240323</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>100.9566383404025</v>
+        <v>91.38693510057962</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>97.35128523706739</v>
+        <v>88.18147894867069</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>93.91034807456455</v>
+        <v>85.12158399270803</v>
       </c>
     </row>
     <row r="8">
@@ -1213,77 +1213,77 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>124.051519685648</v>
+        <v>111.8598480983708</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>119.3830070320639</v>
+        <v>107.7145594858988</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>114.9333823403975</v>
+        <v>103.7629278890247</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>110.6911845312872</v>
+        <v>99.99482899851662</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>106.6456075409105</v>
+        <v>96.40071666523964</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>102.7864599360024</v>
+        <v>92.9715872698396</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>99.10412719443669</v>
+        <v>89.69894644350242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>13</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>130.8942747613876</v>
+      <c r="B9" s="53" t="n">
+        <v>117.8904800179746</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>125.9149499024515</v>
+        <v>113.4712675274958</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>121.1699720615234</v>
+        <v>109.2593363714852</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>116.6470451513784</v>
+        <v>105.24382633463</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>112.3345767414186</v>
+        <v>101.4144982298997</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>108.2216346349375</v>
+        <v>97.76169559100852</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>104.2979063143088</v>
+        <v>94.27630889429679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>137.7370298371272</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>132.4468927728392</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>127.4065617826492</v>
+      <c r="B10" s="53" t="n">
+        <v>123.9211119375785</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>119.2279755690927</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>114.7557448539457</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>122.6029057714695</v>
+        <v>110.4928236707434</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>118.0235459419266</v>
+        <v>106.4282797945597</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>113.6568093338725</v>
+        <v>102.5518039121774</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>109.491685434181</v>
+        <v>98.85367134509117</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>144.5797849128668</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>138.9788356432268</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>133.643151503775</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>128.5587663915607</v>
+        <v>129.9517438571824</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>124.9846836106897</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>120.2521533364062</v>
+      </c>
+      <c r="E11" s="53" t="n">
+        <v>115.7418210068567</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>123.7125151424347</v>
+        <v>111.4420613592198</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>119.0919840328076</v>
+        <v>107.3419122333463</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>114.6854645540531</v>
+        <v>103.4310337958855</v>
       </c>
     </row>
     <row r="13">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.061639487992485</v>
+        <v>1.066965761854932</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>110.6911845312872</v>
+        <v>99.99482899851662</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>150.09938072533</v>
+        <v>132.2253000521208</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>80.98955809830017</v>
+        <v>75.01840755889674</v>
       </c>
     </row>
     <row r="59">
